--- a/metadata.xlsx
+++ b/metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/firdaws/Documents/fairds_storage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{615848A4-57F7-A14E-BD56-AA9F637DE578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871BDD05-07B0-434D-B1B7-55E652EFB60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="680" windowWidth="30240" windowHeight="18960" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="regex" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,25 @@
     <sheet name="Sample" sheetId="6" r:id="rId6"/>
     <sheet name="Assay" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14137" uniqueCount="2627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14137" uniqueCount="2632">
   <si>
     <t>short hand form</t>
   </si>
@@ -7442,9 +7455,6 @@
   </si>
   <si>
     <t>quality report</t>
-  </si>
-  <si>
-    <t>({URL}|unknown)</t>
   </si>
   <si>
     <t>file://C/</t>
@@ -8076,11 +8086,32 @@
   <si>
     <t>a single-end sequence file after paired-end stitching/assembling of forward and reverse sequences</t>
   </si>
+  <si>
+    <t>({file}|{URL}|NA|{text})</t>
+  </si>
+  <si>
+    <t>({file}|NA)</t>
+  </si>
+  <si>
+    <t>({file}|null|NA)</t>
+  </si>
+  <si>
+    <t>({date}|null|NA)</t>
+  </si>
+  <si>
+    <t>({integer}|unknown)</t>
+  </si>
+  <si>
+    <t>({URL}|{text}|unknown)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
+  </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -8201,7 +8232,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -8225,6 +8256,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -8532,7 +8564,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.1640625" customWidth="1"/>
-    <col min="2" max="2" width="18.1640625" customWidth="1"/>
+    <col min="2" max="2" width="40.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -8881,8 +8913,8 @@
       <c r="A25" t="s">
         <v>522</v>
       </c>
-      <c r="B25" t="s">
-        <v>2614</v>
+      <c r="B25" s="19" t="s">
+        <v>2613</v>
       </c>
     </row>
   </sheetData>
@@ -8898,7 +8930,7 @@
     <col min="1" max="1" width="31.6640625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="38.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.1640625" customWidth="1"/>
     <col min="6" max="6" width="93.1640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9884,7 +9916,7 @@
         <v>335</v>
       </c>
       <c r="B77" t="s">
-        <v>70</v>
+        <v>2629</v>
       </c>
       <c r="E77" t="s">
         <v>336</v>
@@ -10114,7 +10146,7 @@
         <v>390</v>
       </c>
       <c r="B99" t="s">
-        <v>5</v>
+        <v>2627</v>
       </c>
       <c r="C99" t="s">
         <v>391</v>
@@ -10134,7 +10166,7 @@
         <v>395</v>
       </c>
       <c r="B100" t="s">
-        <v>5</v>
+        <v>2628</v>
       </c>
       <c r="C100" t="s">
         <v>396</v>
@@ -12723,7 +12755,7 @@
         <v>997</v>
       </c>
       <c r="B311" t="s">
-        <v>5</v>
+        <v>2626</v>
       </c>
       <c r="C311" t="s">
         <v>391</v>
@@ -12791,7 +12823,7 @@
         <v>1006</v>
       </c>
       <c r="B315" t="s">
-        <v>5</v>
+        <v>2626</v>
       </c>
       <c r="C315" t="s">
         <v>396</v>
@@ -18733,60 +18765,60 @@
         <v>2471</v>
       </c>
       <c r="B809" s="2" t="s">
+        <v>2631</v>
+      </c>
+      <c r="C809" s="6" t="s">
         <v>2472</v>
       </c>
-      <c r="C809" s="6" t="s">
+      <c r="F809" s="2" t="s">
         <v>2473</v>
       </c>
-      <c r="F809" s="2" t="s">
+    </row>
+    <row r="810" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A810" t="s">
         <v>2474</v>
       </c>
-    </row>
-    <row r="810" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A810" s="2" t="s">
-        <v>2475</v>
-      </c>
-      <c r="B810" s="2" t="s">
+      <c r="B810" t="s">
         <v>81</v>
       </c>
       <c r="C810" t="s">
         <v>2055</v>
       </c>
-      <c r="F810" s="2" t="s">
-        <v>2476</v>
+      <c r="F810" t="s">
+        <v>2475</v>
       </c>
     </row>
     <row r="811" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A811" s="2" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B811" s="2" t="s">
+        <v>2631</v>
+      </c>
+      <c r="C811" s="6" t="s">
+        <v>2472</v>
+      </c>
+      <c r="F811" s="2" t="s">
         <v>2477</v>
-      </c>
-      <c r="B811" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C811" s="6" t="s">
-        <v>2473</v>
-      </c>
-      <c r="F811" s="2" t="s">
-        <v>2478</v>
       </c>
     </row>
     <row r="812" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A812" s="2" t="s">
+        <v>2478</v>
+      </c>
+      <c r="B812" s="2" t="s">
+        <v>2631</v>
+      </c>
+      <c r="C812" s="6" t="s">
+        <v>2472</v>
+      </c>
+      <c r="F812" s="2" t="s">
         <v>2479</v>
-      </c>
-      <c r="B812" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C812" s="6" t="s">
-        <v>2473</v>
-      </c>
-      <c r="F812" s="2" t="s">
-        <v>2480</v>
       </c>
     </row>
     <row r="814" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A814" s="2" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="B814" s="2" t="s">
         <v>57</v>
@@ -18800,7 +18832,7 @@
     </row>
     <row r="815" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A815" s="2" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="B815" s="2" t="s">
         <v>57</v>
@@ -18814,7 +18846,7 @@
     </row>
     <row r="816" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A816" s="2" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="B816" s="2" t="s">
         <v>57</v>
@@ -18823,26 +18855,26 @@
         <v>195</v>
       </c>
       <c r="F816" s="2" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="817" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A817" s="2" t="s">
+        <v>2484</v>
+      </c>
+      <c r="B817" s="2" t="s">
         <v>2485</v>
       </c>
-      <c r="B817" s="2" t="s">
+      <c r="C817" s="2" t="s">
         <v>2486</v>
       </c>
-      <c r="C817" s="2" t="s">
+      <c r="F817" s="2" t="s">
         <v>2487</v>
-      </c>
-      <c r="F817" s="2" t="s">
-        <v>2488</v>
       </c>
     </row>
     <row r="818" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A818" s="2" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="B818" s="2" t="s">
         <v>57</v>
@@ -18851,26 +18883,26 @@
         <v>58695</v>
       </c>
       <c r="F818" s="2" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="819" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A819" s="2" t="s">
+        <v>2490</v>
+      </c>
+      <c r="B819" s="2" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C819" s="2" t="s">
+        <v>2486</v>
+      </c>
+      <c r="F819" s="2" t="s">
         <v>2491</v>
-      </c>
-      <c r="B819" s="2" t="s">
-        <v>2486</v>
-      </c>
-      <c r="C819" s="2" t="s">
-        <v>2487</v>
-      </c>
-      <c r="F819" s="2" t="s">
-        <v>2492</v>
       </c>
     </row>
     <row r="820" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A820" s="2" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="B820" s="2" t="s">
         <v>57</v>
@@ -18881,7 +18913,7 @@
     </row>
     <row r="822" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A822" s="2" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="B822" s="2" t="s">
         <v>10</v>
@@ -18890,12 +18922,12 @@
         <v>77</v>
       </c>
       <c r="F822" s="2" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="823" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A823" s="2" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="B823" s="2" t="s">
         <v>10</v>
@@ -18904,7 +18936,7 @@
         <v>77</v>
       </c>
       <c r="F823" s="2" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="824" spans="1:6" x14ac:dyDescent="0.2">
@@ -19003,13 +19035,13 @@
         <v>2433</v>
       </c>
       <c r="C831" s="2" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="E831" s="2" t="s">
         <v>185</v>
       </c>
       <c r="F831" s="2" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="832" spans="1:6" x14ac:dyDescent="0.2">
@@ -19030,16 +19062,16 @@
         <v>2419</v>
       </c>
       <c r="B833" s="2" t="s">
+        <v>2499</v>
+      </c>
+      <c r="C833" s="2" t="s">
         <v>2500</v>
-      </c>
-      <c r="C833" s="2" t="s">
-        <v>2501</v>
       </c>
       <c r="E833" s="2" t="s">
         <v>185</v>
       </c>
       <c r="F833" s="2" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="834" spans="1:6" x14ac:dyDescent="0.2">
@@ -19047,14 +19079,14 @@
         <v>2420</v>
       </c>
       <c r="B834" s="2" t="s">
+        <v>2502</v>
+      </c>
+      <c r="C834" s="3" t="s">
         <v>2503</v>
-      </c>
-      <c r="C834" s="3" t="s">
-        <v>2504</v>
       </c>
       <c r="E834" s="2"/>
       <c r="F834" s="2" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="835" spans="1:6" x14ac:dyDescent="0.2">
@@ -19062,16 +19094,16 @@
         <v>2421</v>
       </c>
       <c r="B835" s="2" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="C835" s="2" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="E835" s="2" t="s">
         <v>185</v>
       </c>
       <c r="F835" s="2" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="836" spans="1:6" x14ac:dyDescent="0.2">
@@ -19088,7 +19120,7 @@
         <v>180</v>
       </c>
       <c r="F836" s="2" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="837" spans="1:6" x14ac:dyDescent="0.2">
@@ -19099,10 +19131,10 @@
         <v>183</v>
       </c>
       <c r="C837" s="2" t="s">
+        <v>2508</v>
+      </c>
+      <c r="E837" s="3" t="s">
         <v>2509</v>
-      </c>
-      <c r="E837" s="3" t="s">
-        <v>2510</v>
       </c>
       <c r="F837" s="2"/>
     </row>
@@ -19114,56 +19146,56 @@
         <v>183</v>
       </c>
       <c r="C838" t="s">
+        <v>2510</v>
+      </c>
+      <c r="E838" s="3" t="s">
         <v>2511</v>
       </c>
-      <c r="E838" s="3" t="s">
+      <c r="F838" s="2" t="s">
         <v>2512</v>
-      </c>
-      <c r="F838" s="2" t="s">
-        <v>2513</v>
       </c>
     </row>
     <row r="839" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A839" s="2" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="B839" s="2" t="s">
         <v>183</v>
       </c>
       <c r="E839" s="3"/>
       <c r="F839" s="2" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="840" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A840" s="2" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B840" s="2" t="s">
         <v>183</v>
       </c>
       <c r="E840" s="3"/>
       <c r="F840" s="2" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="841" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A841" s="2" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="B841" t="s">
         <v>183</v>
       </c>
       <c r="E841" t="s">
+        <v>2518</v>
+      </c>
+      <c r="F841" t="s">
         <v>2519</v>
-      </c>
-      <c r="F841" t="s">
-        <v>2520</v>
       </c>
     </row>
     <row r="842" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A842" s="2" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="B842" s="2" t="s">
         <v>2433</v>
@@ -19175,12 +19207,12 @@
         <v>190</v>
       </c>
       <c r="F842" s="2" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="843" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A843" s="2" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="B843" s="2" t="s">
         <v>2433</v>
@@ -19192,27 +19224,27 @@
         <v>190</v>
       </c>
       <c r="F843" s="2" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="844" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A844" s="2" t="s">
+        <v>2523</v>
+      </c>
+      <c r="B844" s="2" t="s">
         <v>2524</v>
       </c>
-      <c r="B844" s="2" t="s">
+      <c r="C844" s="2" t="s">
         <v>2525</v>
-      </c>
-      <c r="C844" s="2" t="s">
-        <v>2526</v>
       </c>
       <c r="E844" s="2"/>
       <c r="F844" s="2" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="845" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A845" s="2" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="B845" s="2" t="s">
         <v>840</v>
@@ -19221,54 +19253,54 @@
         <v>1634</v>
       </c>
       <c r="E845" s="3" t="s">
+        <v>2528</v>
+      </c>
+      <c r="F845" s="2" t="s">
         <v>2529</v>
-      </c>
-      <c r="F845" s="2" t="s">
-        <v>2530</v>
       </c>
     </row>
     <row r="846" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A846" s="2" t="s">
+        <v>2530</v>
+      </c>
+      <c r="B846" s="2" t="s">
+        <v>2502</v>
+      </c>
+      <c r="C846" s="2" t="s">
         <v>2531</v>
-      </c>
-      <c r="B846" s="2" t="s">
-        <v>2503</v>
-      </c>
-      <c r="C846" s="2" t="s">
-        <v>2532</v>
       </c>
       <c r="E846" s="2"/>
       <c r="F846" s="2" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="847" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A847" s="2" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="B847" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C847" s="2" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="E847" s="2"/>
       <c r="F847" s="2" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="848" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A848" s="2" t="s">
+        <v>2536</v>
+      </c>
+      <c r="B848" s="2" t="s">
         <v>2537</v>
-      </c>
-      <c r="B848" s="2" t="s">
-        <v>2538</v>
       </c>
       <c r="C848">
         <v>1993</v>
       </c>
       <c r="F848" s="2" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="849" spans="1:6" x14ac:dyDescent="0.2">
@@ -19278,13 +19310,13 @@
     </row>
     <row r="850" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A850" s="2" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="B850" s="2" t="s">
         <v>76</v>
       </c>
       <c r="F850" s="2" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="851" spans="1:6" x14ac:dyDescent="0.2">
@@ -19294,7 +19326,7 @@
     </row>
     <row r="852" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A852" s="2" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
       <c r="B852" s="2" t="s">
         <v>183</v>
@@ -19303,7 +19335,7 @@
     </row>
     <row r="853" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A853" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
       <c r="B853" s="2" t="s">
         <v>183</v>
@@ -19312,13 +19344,13 @@
     </row>
     <row r="854" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A854" t="s">
+        <v>2624</v>
+      </c>
+      <c r="B854" s="2" t="s">
+        <v>2502</v>
+      </c>
+      <c r="F854" t="s">
         <v>2625</v>
-      </c>
-      <c r="B854" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="F854" t="s">
-        <v>2626</v>
       </c>
     </row>
     <row r="856" spans="1:6" x14ac:dyDescent="0.2">
@@ -19329,7 +19361,7 @@
         <v>10</v>
       </c>
       <c r="C856" s="2" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="857" spans="1:6" x14ac:dyDescent="0.2">
@@ -19337,7 +19369,7 @@
         <v>2424</v>
       </c>
       <c r="B857" s="2" t="s">
-        <v>28</v>
+        <v>2630</v>
       </c>
       <c r="C857">
         <v>25</v>
@@ -19351,15 +19383,15 @@
         <v>10</v>
       </c>
       <c r="C858" t="s">
+        <v>2539</v>
+      </c>
+      <c r="F858" t="s">
         <v>2540</v>
-      </c>
-      <c r="F858" t="s">
-        <v>2541</v>
       </c>
     </row>
     <row r="860" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A860" s="2" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="B860" s="2" t="s">
         <v>10</v>
@@ -19367,37 +19399,37 @@
     </row>
     <row r="861" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A861" s="2" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B861" s="2" t="s">
         <v>2555</v>
       </c>
-      <c r="B861" s="2" t="s">
+      <c r="C861" t="s">
         <v>2556</v>
-      </c>
-      <c r="C861" t="s">
-        <v>2557</v>
       </c>
     </row>
     <row r="862" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A862" s="2" t="s">
+        <v>2557</v>
+      </c>
+      <c r="B862" s="2" t="s">
         <v>2558</v>
-      </c>
-      <c r="B862" s="2" t="s">
-        <v>2559</v>
       </c>
     </row>
     <row r="863" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A863" s="2" t="s">
+        <v>2559</v>
+      </c>
+      <c r="B863" s="2" t="s">
         <v>2560</v>
-      </c>
-      <c r="B863" s="2" t="s">
-        <v>2561</v>
       </c>
     </row>
     <row r="864" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A864" s="2" t="s">
+        <v>2561</v>
+      </c>
+      <c r="B864" s="2" t="s">
         <v>2562</v>
-      </c>
-      <c r="B864" s="2" t="s">
-        <v>2563</v>
       </c>
       <c r="C864" t="s">
         <v>2437</v>
@@ -19405,18 +19437,18 @@
     </row>
     <row r="865" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A865" s="2" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B865" s="2" t="s">
         <v>2564</v>
       </c>
-      <c r="B865" s="2" t="s">
+      <c r="E865" s="12" t="s">
         <v>2565</v>
-      </c>
-      <c r="E865" s="12" t="s">
-        <v>2566</v>
       </c>
     </row>
     <row r="866" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A866" s="2" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="B866" s="2" t="s">
         <v>52</v>
@@ -19430,13 +19462,13 @@
         <v>10</v>
       </c>
       <c r="C868" t="s">
+        <v>2567</v>
+      </c>
+      <c r="E868" s="13" t="s">
         <v>2568</v>
       </c>
-      <c r="E868" s="13" t="s">
+      <c r="F868" t="s">
         <v>2569</v>
-      </c>
-      <c r="F868" t="s">
-        <v>2570</v>
       </c>
     </row>
     <row r="869" spans="1:6" x14ac:dyDescent="0.2">
@@ -19458,206 +19490,206 @@
         <v>1398</v>
       </c>
       <c r="E870" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="871" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A871" s="2" t="s">
-        <v>2617</v>
+        <v>2616</v>
       </c>
       <c r="B871" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C871" t="s">
+        <v>2617</v>
+      </c>
+      <c r="F871" t="s">
         <v>2618</v>
-      </c>
-      <c r="F871" t="s">
-        <v>2619</v>
       </c>
     </row>
     <row r="873" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A873" s="11" t="s">
-        <v>2572</v>
+        <v>2571</v>
       </c>
       <c r="B873" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C873" s="14" t="s">
+        <v>2572</v>
+      </c>
+      <c r="E873" s="13" t="s">
         <v>2573</v>
       </c>
-      <c r="E873" s="13" t="s">
+      <c r="F873" s="15" t="s">
         <v>2574</v>
-      </c>
-      <c r="F873" s="15" t="s">
-        <v>2575</v>
       </c>
     </row>
     <row r="874" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A874" s="11" t="s">
-        <v>2576</v>
+        <v>2575</v>
       </c>
       <c r="B874" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C874" s="14" t="s">
+        <v>2576</v>
+      </c>
+      <c r="E874" s="13" t="s">
         <v>2577</v>
       </c>
-      <c r="E874" s="13" t="s">
+      <c r="F874" t="s">
         <v>2578</v>
-      </c>
-      <c r="F874" t="s">
-        <v>2579</v>
       </c>
     </row>
     <row r="875" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A875" s="11" t="s">
-        <v>2580</v>
+        <v>2579</v>
       </c>
       <c r="B875" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C875" s="14" t="s">
+        <v>2580</v>
+      </c>
+      <c r="E875" s="13" t="s">
         <v>2581</v>
       </c>
-      <c r="E875" s="13" t="s">
+      <c r="F875" t="s">
         <v>2582</v>
-      </c>
-      <c r="F875" t="s">
-        <v>2583</v>
       </c>
     </row>
     <row r="876" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A876" s="11" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="B876" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C876" s="14" t="s">
+        <v>2584</v>
+      </c>
+      <c r="E876" s="13" t="s">
         <v>2585</v>
       </c>
-      <c r="E876" s="13" t="s">
+      <c r="F876" t="s">
         <v>2586</v>
-      </c>
-      <c r="F876" t="s">
-        <v>2587</v>
       </c>
     </row>
     <row r="877" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A877" s="11" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
       <c r="B877" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C877" s="14" t="s">
+        <v>2588</v>
+      </c>
+      <c r="E877" s="13" t="s">
         <v>2589</v>
       </c>
-      <c r="E877" s="13" t="s">
+      <c r="F877" t="s">
         <v>2590</v>
-      </c>
-      <c r="F877" t="s">
-        <v>2591</v>
       </c>
     </row>
     <row r="878" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A878" s="11" t="s">
-        <v>2592</v>
+        <v>2591</v>
       </c>
       <c r="B878" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C878" s="14" t="s">
+        <v>2592</v>
+      </c>
+      <c r="E878" s="13" t="s">
         <v>2593</v>
       </c>
-      <c r="E878" s="13" t="s">
+      <c r="F878" t="s">
         <v>2594</v>
-      </c>
-      <c r="F878" t="s">
-        <v>2595</v>
       </c>
     </row>
     <row r="879" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A879" s="11" t="s">
-        <v>2596</v>
+        <v>2595</v>
       </c>
       <c r="B879" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C879" s="14" t="s">
+        <v>2596</v>
+      </c>
+      <c r="E879" s="13" t="s">
         <v>2597</v>
       </c>
-      <c r="E879" s="13" t="s">
+      <c r="F879" t="s">
         <v>2598</v>
-      </c>
-      <c r="F879" t="s">
-        <v>2599</v>
       </c>
     </row>
     <row r="880" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A880" s="11" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="B880" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C880" s="14" t="s">
+        <v>2600</v>
+      </c>
+      <c r="E880" s="13" t="s">
         <v>2601</v>
       </c>
-      <c r="E880" s="13" t="s">
+      <c r="F880" t="s">
         <v>2602</v>
-      </c>
-      <c r="F880" t="s">
-        <v>2603</v>
       </c>
     </row>
     <row r="881" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A881" s="11" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
       <c r="B881" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C881" s="14" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
       <c r="E881" s="13"/>
       <c r="F881" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="882" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A882" s="11" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
       <c r="B882" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C882" s="14" t="s">
+        <v>2607</v>
+      </c>
+      <c r="E882" s="13" t="s">
         <v>2608</v>
       </c>
-      <c r="E882" s="13" t="s">
+      <c r="F882" t="s">
         <v>2609</v>
-      </c>
-      <c r="F882" t="s">
-        <v>2610</v>
       </c>
     </row>
     <row r="883" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A883" s="11" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="B883" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C883" s="14" t="s">
-        <v>2577</v>
+        <v>2576</v>
       </c>
       <c r="E883" s="13" t="s">
+        <v>2611</v>
+      </c>
+      <c r="F883" t="s">
         <v>2612</v>
-      </c>
-      <c r="F883" t="s">
-        <v>2613</v>
       </c>
     </row>
   </sheetData>
@@ -19692,7 +19724,7 @@
         <v>2321</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="F1" s="18" t="s">
         <v>2</v>
@@ -19918,7 +19950,7 @@
         <v>2321</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="F1" s="18" t="s">
         <v>2</v>
@@ -20228,7 +20260,7 @@
         <v>2321</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="F1" s="18" t="s">
         <v>2</v>
@@ -20836,7 +20868,7 @@
         <v>2321</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="F1" s="18" t="s">
         <v>2</v>
@@ -54517,7 +54549,7 @@
         <v>2335</v>
       </c>
       <c r="B2413" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="C2413" t="s">
         <v>2428</v>
@@ -54531,7 +54563,7 @@
         <v>2335</v>
       </c>
       <c r="B2414" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="C2414" t="s">
         <v>2429</v>
@@ -54545,7 +54577,7 @@
         <v>2335</v>
       </c>
       <c r="B2415" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="C2415" t="s">
         <v>2430</v>
@@ -54559,10 +54591,10 @@
         <v>2335</v>
       </c>
       <c r="B2416" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="C2416" t="s">
-        <v>2616</v>
+        <v>2615</v>
       </c>
       <c r="D2416" t="s">
         <v>2324</v>
@@ -54573,10 +54605,10 @@
         <v>2335</v>
       </c>
       <c r="B2417" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="C2417" t="s">
-        <v>2617</v>
+        <v>2616</v>
       </c>
       <c r="D2417" t="s">
         <v>2324</v>
@@ -54587,10 +54619,10 @@
         <v>2335</v>
       </c>
       <c r="B2418" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="C2418" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="D2418" t="s">
         <v>2325</v>
@@ -54624,7 +54656,7 @@
         <v>2321</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="F1" s="18" t="s">
         <v>2</v>
@@ -55895,7 +55927,7 @@
         <v>2398</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>2442</v>
@@ -55909,7 +55941,7 @@
         <v>2398</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>2444</v>
@@ -55923,7 +55955,7 @@
         <v>2398</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>2447</v>
@@ -55937,7 +55969,7 @@
         <v>2398</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>2449</v>
@@ -55951,7 +55983,7 @@
         <v>2398</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>2451</v>
@@ -55965,7 +55997,7 @@
         <v>2398</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>2454</v>
@@ -55979,7 +56011,7 @@
         <v>2398</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>2456</v>
@@ -55993,7 +56025,7 @@
         <v>2398</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>2458</v>
@@ -56007,7 +56039,7 @@
         <v>2398</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>2462</v>
@@ -56021,7 +56053,7 @@
         <v>2398</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>2466</v>
@@ -56035,7 +56067,7 @@
         <v>2398</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>2469</v>
@@ -56049,7 +56081,7 @@
         <v>2398</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>2471</v>
@@ -56063,10 +56095,10 @@
         <v>2398</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>2324</v>
@@ -56077,10 +56109,10 @@
         <v>2398</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>2324</v>
@@ -56091,10 +56123,10 @@
         <v>2398</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>2327</v>
@@ -56105,10 +56137,10 @@
         <v>2398</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>2327</v>
@@ -56119,10 +56151,10 @@
         <v>2398</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>2327</v>
@@ -56133,10 +56165,10 @@
         <v>2398</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>2324</v>
@@ -56147,10 +56179,10 @@
         <v>2398</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>2324</v>
@@ -56161,10 +56193,10 @@
         <v>2398</v>
       </c>
       <c r="B127" s="2" t="s">
+        <v>2541</v>
+      </c>
+      <c r="C127" s="2" t="s">
         <v>2542</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>2543</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>2327</v>
@@ -56180,7 +56212,7 @@
         <v>2398</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>2442</v>
@@ -56194,7 +56226,7 @@
         <v>2398</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>2444</v>
@@ -56208,7 +56240,7 @@
         <v>2398</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>2458</v>
@@ -56222,7 +56254,7 @@
         <v>2398</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>2462</v>
@@ -56236,7 +56268,7 @@
         <v>2398</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>2466</v>
@@ -56250,7 +56282,7 @@
         <v>2398</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>2469</v>
@@ -56264,7 +56296,7 @@
         <v>2398</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>2471</v>
@@ -56278,10 +56310,10 @@
         <v>2398</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>2324</v>
@@ -56292,10 +56324,10 @@
         <v>2398</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>2324</v>
@@ -56306,10 +56338,10 @@
         <v>2398</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>2327</v>
@@ -56320,10 +56352,10 @@
         <v>2398</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>2327</v>
@@ -56334,10 +56366,10 @@
         <v>2398</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>2327</v>
@@ -56348,10 +56380,10 @@
         <v>2398</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>2324</v>
@@ -56362,10 +56394,10 @@
         <v>2398</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>2324</v>
@@ -56376,10 +56408,10 @@
         <v>2398</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>2327</v>
@@ -56395,7 +56427,7 @@
         <v>2398</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>2442</v>
@@ -56409,7 +56441,7 @@
         <v>2398</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>2444</v>
@@ -56423,7 +56455,7 @@
         <v>2398</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>2447</v>
@@ -56437,7 +56469,7 @@
         <v>2398</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>2449</v>
@@ -56451,7 +56483,7 @@
         <v>2398</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>2451</v>
@@ -56465,7 +56497,7 @@
         <v>2398</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>2454</v>
@@ -56479,7 +56511,7 @@
         <v>2398</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>2456</v>
@@ -56493,7 +56525,7 @@
         <v>2398</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>2458</v>
@@ -56507,7 +56539,7 @@
         <v>2398</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>2462</v>
@@ -56521,10 +56553,10 @@
         <v>2398</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>2324</v>
@@ -56535,10 +56567,10 @@
         <v>2398</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>2324</v>
@@ -56549,10 +56581,10 @@
         <v>2398</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="D156" s="9" t="s">
         <v>2327</v>
@@ -56563,10 +56595,10 @@
         <v>2398</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="D157" s="9" t="s">
         <v>2327</v>
@@ -56577,10 +56609,10 @@
         <v>2398</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>2325</v>
@@ -56591,10 +56623,10 @@
         <v>2398</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>2325</v>
@@ -56605,10 +56637,10 @@
         <v>2398</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>2325</v>
@@ -56619,7 +56651,7 @@
         <v>2398</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>2471</v>
@@ -56633,10 +56665,10 @@
         <v>2398</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>2324</v>
@@ -56647,10 +56679,10 @@
         <v>2398</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>2324</v>
@@ -56661,10 +56693,10 @@
         <v>2398</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>2327</v>
@@ -56675,10 +56707,10 @@
         <v>2398</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>2327</v>
@@ -56694,7 +56726,7 @@
         <v>2398</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>2442</v>
@@ -56708,7 +56740,7 @@
         <v>2398</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>2444</v>
@@ -56722,7 +56754,7 @@
         <v>2398</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>2447</v>
@@ -56736,7 +56768,7 @@
         <v>2398</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>2449</v>
@@ -56750,7 +56782,7 @@
         <v>2398</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>2451</v>
@@ -56764,7 +56796,7 @@
         <v>2398</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>2454</v>
@@ -56778,7 +56810,7 @@
         <v>2398</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>2456</v>
@@ -56792,7 +56824,7 @@
         <v>2398</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>2458</v>
@@ -56806,7 +56838,7 @@
         <v>2398</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>2462</v>
@@ -56820,10 +56852,10 @@
         <v>2398</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>2324</v>
@@ -56834,10 +56866,10 @@
         <v>2398</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>2325</v>
@@ -56848,7 +56880,7 @@
         <v>2398</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>2471</v>
@@ -56862,10 +56894,10 @@
         <v>2398</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C179" s="9" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>2324</v>
@@ -56876,10 +56908,10 @@
         <v>2398</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>2324</v>
@@ -56890,10 +56922,10 @@
         <v>2398</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>2327</v>
@@ -56904,10 +56936,10 @@
         <v>2398</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>2327</v>
@@ -56919,10 +56951,10 @@
         <v>2398</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>2327</v>
@@ -56934,10 +56966,10 @@
         <v>2398</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>2327</v>
@@ -56954,7 +56986,7 @@
         <v>2398</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>2442</v>
@@ -56968,7 +57000,7 @@
         <v>2398</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>2444</v>
@@ -56982,7 +57014,7 @@
         <v>2398</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>2447</v>
@@ -56996,7 +57028,7 @@
         <v>2398</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>2449</v>
@@ -57010,7 +57042,7 @@
         <v>2398</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>2451</v>
@@ -57024,7 +57056,7 @@
         <v>2398</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>2454</v>
@@ -57038,7 +57070,7 @@
         <v>2398</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>2456</v>
@@ -57052,7 +57084,7 @@
         <v>2398</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>2458</v>
@@ -57066,7 +57098,7 @@
         <v>2398</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>2462</v>
@@ -57080,10 +57112,10 @@
         <v>2398</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>2324</v>
@@ -57094,10 +57126,10 @@
         <v>2398</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>2325</v>
@@ -57108,7 +57140,7 @@
         <v>2398</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>2471</v>
@@ -57122,10 +57154,10 @@
         <v>2398</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C198" s="9" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>2324</v>
@@ -57136,7 +57168,7 @@
         <v>2398</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>2435</v>
@@ -57150,10 +57182,10 @@
         <v>2398</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>2324</v>
@@ -57164,10 +57196,10 @@
         <v>2398</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>2327</v>
@@ -57178,10 +57210,10 @@
         <v>2398</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>2327</v>
@@ -57192,7 +57224,7 @@
         <v>2398</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>1153</v>
@@ -57206,10 +57238,10 @@
         <v>2398</v>
       </c>
       <c r="B204" s="2" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C204" s="2" t="s">
         <v>2547</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>2548</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>2327</v>
@@ -57225,7 +57257,7 @@
         <v>2398</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>2442</v>
@@ -57239,7 +57271,7 @@
         <v>2398</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>2444</v>
@@ -57253,7 +57285,7 @@
         <v>2398</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>2447</v>
@@ -57267,7 +57299,7 @@
         <v>2398</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>2449</v>
@@ -57281,7 +57313,7 @@
         <v>2398</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>2451</v>
@@ -57295,7 +57327,7 @@
         <v>2398</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>2454</v>
@@ -57309,7 +57341,7 @@
         <v>2398</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>2456</v>
@@ -57323,7 +57355,7 @@
         <v>2398</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>2458</v>
@@ -57337,7 +57369,7 @@
         <v>2398</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>2462</v>
@@ -57351,10 +57383,10 @@
         <v>2398</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>2324</v>
@@ -57365,10 +57397,10 @@
         <v>2398</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>2325</v>
@@ -57379,7 +57411,7 @@
         <v>2398</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>2471</v>
@@ -57393,10 +57425,10 @@
         <v>2398</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C218" s="9" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>2324</v>
@@ -57407,10 +57439,10 @@
         <v>2398</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>2324</v>
@@ -57421,10 +57453,10 @@
         <v>2398</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>2327</v>
@@ -57435,10 +57467,10 @@
         <v>2398</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>2327</v>
@@ -57449,7 +57481,7 @@
         <v>2398</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>1153</v>
@@ -57463,10 +57495,10 @@
         <v>2398</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>2327</v>
@@ -57482,10 +57514,10 @@
         <v>2398</v>
       </c>
       <c r="B225" s="2" t="s">
+        <v>2549</v>
+      </c>
+      <c r="C225" s="2" t="s">
         <v>2550</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>2551</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>2324</v>
@@ -57496,7 +57528,7 @@
         <v>2398</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>2444</v>
@@ -57510,7 +57542,7 @@
         <v>2398</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>2447</v>
@@ -57524,7 +57556,7 @@
         <v>2398</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>2449</v>
@@ -57538,7 +57570,7 @@
         <v>2398</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>2451</v>
@@ -57552,7 +57584,7 @@
         <v>2398</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>2454</v>
@@ -57566,7 +57598,7 @@
         <v>2398</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>2456</v>
@@ -57580,7 +57612,7 @@
         <v>2398</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>2458</v>
@@ -57594,7 +57626,7 @@
         <v>2398</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>2462</v>
@@ -57608,7 +57640,7 @@
         <v>2398</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>2471</v>
@@ -57622,10 +57654,10 @@
         <v>2398</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C235" s="9" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>2324</v>
@@ -57636,10 +57668,10 @@
         <v>2398</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>2324</v>
@@ -57650,10 +57682,10 @@
         <v>2398</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>2327</v>
@@ -57669,10 +57701,10 @@
         <v>2398</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>2324</v>
@@ -57683,7 +57715,7 @@
         <v>2398</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>2444</v>
@@ -57697,7 +57729,7 @@
         <v>2398</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>2447</v>
@@ -57711,7 +57743,7 @@
         <v>2398</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>2449</v>
@@ -57725,7 +57757,7 @@
         <v>2398</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>2451</v>
@@ -57739,7 +57771,7 @@
         <v>2398</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>2454</v>
@@ -57753,7 +57785,7 @@
         <v>2398</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>2456</v>
@@ -57767,7 +57799,7 @@
         <v>2398</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>2458</v>
@@ -57781,7 +57813,7 @@
         <v>2398</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>2462</v>
@@ -57795,10 +57827,10 @@
         <v>2398</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>2324</v>
@@ -57809,10 +57841,10 @@
         <v>2398</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>2325</v>
@@ -57823,7 +57855,7 @@
         <v>2398</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>2471</v>
@@ -57837,10 +57869,10 @@
         <v>2398</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C251" s="9" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>2324</v>
@@ -57851,10 +57883,10 @@
         <v>2398</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>2324</v>
@@ -57865,10 +57897,10 @@
         <v>2398</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>2327</v>
@@ -57879,10 +57911,10 @@
         <v>2398</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>2327</v>
@@ -57893,7 +57925,7 @@
         <v>2398</v>
       </c>
       <c r="B256" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C256" s="10" t="s">
         <v>2442</v>
@@ -57907,7 +57939,7 @@
         <v>2398</v>
       </c>
       <c r="B257" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C257" s="10" t="s">
         <v>2444</v>
@@ -57921,7 +57953,7 @@
         <v>2398</v>
       </c>
       <c r="B258" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C258" s="10" t="s">
         <v>2447</v>
@@ -57935,7 +57967,7 @@
         <v>2398</v>
       </c>
       <c r="B259" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C259" s="10" t="s">
         <v>2449</v>
@@ -57949,7 +57981,7 @@
         <v>2398</v>
       </c>
       <c r="B260" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C260" s="10" t="s">
         <v>2451</v>
@@ -57963,7 +57995,7 @@
         <v>2398</v>
       </c>
       <c r="B261" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C261" s="10" t="s">
         <v>2454</v>
@@ -57977,7 +58009,7 @@
         <v>2398</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C262" s="10" t="s">
         <v>2456</v>
@@ -57991,7 +58023,7 @@
         <v>2398</v>
       </c>
       <c r="B263" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C263" s="10" t="s">
         <v>2458</v>
@@ -58005,7 +58037,7 @@
         <v>2398</v>
       </c>
       <c r="B264" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C264" s="10" t="s">
         <v>2462</v>
@@ -58019,10 +58051,10 @@
         <v>2398</v>
       </c>
       <c r="B265" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C265" s="10" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="D265" s="10" t="s">
         <v>2324</v>
@@ -58033,10 +58065,10 @@
         <v>2398</v>
       </c>
       <c r="B266" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C266" s="10" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="D266" s="10" t="s">
         <v>2324</v>
@@ -58047,10 +58079,10 @@
         <v>2398</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="D267" s="9" t="s">
         <v>2327</v>
@@ -58061,10 +58093,10 @@
         <v>2398</v>
       </c>
       <c r="B268" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C268" s="10" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="D268" s="9" t="s">
         <v>2327</v>
@@ -58075,10 +58107,10 @@
         <v>2398</v>
       </c>
       <c r="B269" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C269" s="10" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="D269" s="10" t="s">
         <v>2325</v>
@@ -58089,10 +58121,10 @@
         <v>2398</v>
       </c>
       <c r="B270" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C270" s="10" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="D270" s="10" t="s">
         <v>2325</v>
@@ -58103,7 +58135,7 @@
         <v>2398</v>
       </c>
       <c r="B271" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C271" s="10" t="s">
         <v>2471</v>
@@ -58117,10 +58149,10 @@
         <v>2398</v>
       </c>
       <c r="B272" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C272" s="10" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="D272" s="10" t="s">
         <v>2324</v>
@@ -58131,10 +58163,10 @@
         <v>2398</v>
       </c>
       <c r="B273" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C273" s="10" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="D273" s="10" t="s">
         <v>2324</v>
@@ -58145,10 +58177,10 @@
         <v>2398</v>
       </c>
       <c r="B274" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C274" s="10" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="D274" s="10" t="s">
         <v>2327</v>
@@ -58159,10 +58191,10 @@
         <v>2398</v>
       </c>
       <c r="B275" s="10" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C275" s="10" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="D275" s="10" t="s">
         <v>2327</v>
@@ -58173,7 +58205,7 @@
         <v>2398</v>
       </c>
       <c r="B278" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C278" t="s">
         <v>390</v>
@@ -58187,7 +58219,7 @@
         <v>2398</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C279" t="s">
         <v>395</v>
@@ -58201,10 +58233,10 @@
         <v>2398</v>
       </c>
       <c r="B280" s="10" t="s">
+        <v>2620</v>
+      </c>
+      <c r="C280" t="s">
         <v>2621</v>
-      </c>
-      <c r="C280" t="s">
-        <v>2622</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>2324</v>
@@ -58215,7 +58247,7 @@
         <v>2398</v>
       </c>
       <c r="B281" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C281" t="s">
         <v>1441</v>
@@ -58229,7 +58261,7 @@
         <v>2398</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C282" t="s">
         <v>1366</v>
@@ -58243,7 +58275,7 @@
         <v>2398</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C283" t="s">
         <v>1830</v>
@@ -58257,7 +58289,7 @@
         <v>2398</v>
       </c>
       <c r="B284" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C284" t="s">
         <v>1000</v>
@@ -58271,7 +58303,7 @@
         <v>2398</v>
       </c>
       <c r="B285" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C285" t="s">
         <v>587</v>
@@ -58285,7 +58317,7 @@
         <v>2398</v>
       </c>
       <c r="B286" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C286" t="s">
         <v>1435</v>
@@ -58299,7 +58331,7 @@
         <v>2398</v>
       </c>
       <c r="B287" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C287" t="s">
         <v>997</v>
@@ -58313,7 +58345,7 @@
         <v>2398</v>
       </c>
       <c r="B288" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C288" t="s">
         <v>1006</v>
@@ -58327,7 +58359,7 @@
         <v>2398</v>
       </c>
       <c r="B289" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C289" t="s">
         <v>941</v>
@@ -58341,7 +58373,7 @@
         <v>2398</v>
       </c>
       <c r="B290" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C290" t="s">
         <v>1322</v>
@@ -58355,7 +58387,7 @@
         <v>2398</v>
       </c>
       <c r="B291" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C291" t="s">
         <v>946</v>
@@ -58369,7 +58401,7 @@
         <v>2398</v>
       </c>
       <c r="B292" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C292" t="s">
         <v>1018</v>
@@ -58383,7 +58415,7 @@
         <v>2398</v>
       </c>
       <c r="B293" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C293" t="s">
         <v>1012</v>
@@ -58397,7 +58429,7 @@
         <v>2398</v>
       </c>
       <c r="B294" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C294" t="s">
         <v>1021</v>
@@ -58411,10 +58443,10 @@
         <v>2398</v>
       </c>
       <c r="B295" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C295" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>2327</v>
@@ -58425,10 +58457,10 @@
         <v>2398</v>
       </c>
       <c r="B296" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C296" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>2327</v>
@@ -58439,10 +58471,10 @@
         <v>2398</v>
       </c>
       <c r="B297" s="10" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C297" t="s">
-        <v>2625</v>
+        <v>2624</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>2327</v>
